--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.86308978132732</v>
+        <v>2.740252089465689</v>
       </c>
       <c r="D2" t="n">
-        <v>17.78090263746518</v>
+        <v>2.889396678588092</v>
       </c>
       <c r="E2" t="n">
-        <v>21.6189337878713</v>
+        <v>3.513076740529086</v>
       </c>
       <c r="F2" t="n">
-        <v>4.582209856151616</v>
+        <v>0.7446091016246376</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.43793482600079</v>
+        <v>2.346164409225128</v>
       </c>
       <c r="D3" t="n">
-        <v>14.76546171012793</v>
+        <v>2.399387527895789</v>
       </c>
       <c r="E3" t="n">
-        <v>21.6189337878713</v>
+        <v>3.513076740529086</v>
       </c>
       <c r="F3" t="n">
-        <v>4.582209856151616</v>
+        <v>0.7446091016246376</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.39309085908483</v>
+        <v>2.663877264601285</v>
       </c>
       <c r="D4" t="n">
-        <v>16.95998276768846</v>
+        <v>2.755997199749375</v>
       </c>
       <c r="E4" t="n">
-        <v>21.6189337878713</v>
+        <v>3.513076740529086</v>
       </c>
       <c r="F4" t="n">
-        <v>4.582209856151616</v>
+        <v>0.7446091016246376</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>58.67270339576267</v>
+        <v>9.534314301811435</v>
       </c>
       <c r="D5" t="n">
-        <v>16.58322306763614</v>
+        <v>2.694773748490873</v>
       </c>
       <c r="E5" t="n">
-        <v>21.6189337878713</v>
+        <v>3.513076740529086</v>
       </c>
       <c r="F5" t="n">
-        <v>4.582209856151616</v>
+        <v>0.7446091016246376</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>62.72101827421384</v>
+        <v>10.19216546955975</v>
       </c>
       <c r="D6" t="n">
-        <v>27.01223804946979</v>
+        <v>4.389488683038842</v>
       </c>
       <c r="E6" t="n">
-        <v>21.6189337878713</v>
+        <v>3.513076740529086</v>
       </c>
       <c r="F6" t="n">
-        <v>4.582209856151616</v>
+        <v>0.7446091016246376</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.33886137155723</v>
+        <v>2.00506497287805</v>
       </c>
       <c r="D7" t="n">
-        <v>12.31945153372394</v>
+        <v>2.00191087423014</v>
       </c>
       <c r="E7" t="n">
-        <v>21.6189337878713</v>
+        <v>3.513076740529086</v>
       </c>
       <c r="F7" t="n">
-        <v>4.582209856151616</v>
+        <v>0.7446091016246376</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
